--- a/data-manipulation-scripts/sheets-cleanup/sheets/SOQUETE FAROL - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/SOQUETE FAROL - 02_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -41,24 +41,6 @@
   </si>
   <si>
     <t>SOQUETE FAROL SMARTFOX C100 BIZ</t>
-  </si>
-  <si>
-    <t>7893986435675</t>
-  </si>
-  <si>
-    <t>REPARO CHICOTE PEÇA+ TITAN/ YBR/ YES</t>
-  </si>
-  <si>
-    <t>7893986435583</t>
-  </si>
-  <si>
-    <t>REPARO CHICOTE PEÇA+ BIZ/ POP/ TITAN/ YES</t>
-  </si>
-  <si>
-    <t>7908305613297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR 4 PINOS MHX </t>
   </si>
   <si>
     <t>7899468091384</t>
@@ -391,7 +373,9 @@
       <c r="C2" s="2">
         <v>10.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -403,7 +387,9 @@
       <c r="C3" s="2">
         <v>4.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>12.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -415,7 +401,9 @@
       <c r="C4" s="2">
         <v>2.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -425,10 +413,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D5" s="2">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="6">
@@ -441,7 +429,9 @@
       <c r="C6" s="2">
         <v>2.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -451,9 +441,11 @@
         <v>15</v>
       </c>
       <c r="C7" s="2">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>13.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -465,50 +457,32 @@
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2">
+        <v>12.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2.0</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>13.0</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="A12" s="4"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -6417,38 +6391,14 @@
       <c r="C996" s="3"/>
       <c r="D996" s="3"/>
     </row>
-    <row r="997">
-      <c r="A997" s="4"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="4"/>
-      <c r="B998" s="3"/>
-      <c r="C998" s="3"/>
-      <c r="D998" s="3"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="4"/>
-      <c r="B999" s="3"/>
-      <c r="C999" s="3"/>
-      <c r="D999" s="3"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A996">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A996">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
